--- a/test_data/te2ss3t.xlsx
+++ b/test_data/te2ss3t.xlsx
@@ -1495,11 +1495,7 @@
     <s:row r="2" ht="19.5" customHeight="1" spans="1:6">
       <s:c r="A2" s="4"/>
       <s:c r="B2" s="4"/>
-      <s:c r="D2" s="5" t="inlineStr">
-        <s:is>
-          <s:t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</s:t>
-        </s:is>
-      </s:c>
+      <s:c r="D2" s="5"/>
       <s:c r="E2" s="5"/>
       <s:c r="F2" s="5"/>
     </s:row>
@@ -1515,7 +1511,44 @@
       <s:c r="E4" s="5"/>
       <s:c r="F4" s="5"/>
     </s:row>
-    <s:row r="5"/>
+    <s:row r="5">
+      <s:c r="A5">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="B5" t="inlineStr">
+        <s:is>
+          <s:t>U1</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C5">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="D5" t="inlineStr">
+        <s:is>
+          <s:t>Linear</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E5" t="inlineStr">
+        <s:is>
+          <s:t>LTC3780EG#PBF</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F5" t="inlineStr">
+        <s:is>
+          <s:t>IC BUCK-BOOST CONV 24-SSOP</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G5" t="inlineStr">
+        <s:is>
+          <s:t>24-SSOP</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H5" t="inlineStr">
+        <s:is>
+          <s:t>SMD</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
     <s:row r="6" ht="28.5" customHeight="1" spans="1:9">
       <s:c r="A6" s="6" t="inlineStr">
         <s:is>
@@ -1565,89 +1598,89 @@
     </s:row>
     <s:row r="7" spans="1:9">
       <s:c r="A7" s="9">
-        <s:v>1</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="B7" s="10" t="inlineStr">
         <s:is>
-          <s:t>U1</s:t>
+          <s:t>U2,U4</s:t>
         </s:is>
       </s:c>
       <s:c r="C7" s="9">
-        <s:v>1</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="D7" s="10" t="inlineStr">
         <s:is>
-          <s:t>Linear</s:t>
+          <s:t>Fairchild</s:t>
         </s:is>
       </s:c>
       <s:c r="E7" s="10" t="inlineStr">
         <s:is>
-          <s:t>LTC3780EG#PBF</s:t>
+          <s:t>LM2904M</s:t>
         </s:is>
       </s:c>
       <s:c r="F7" s="11" t="inlineStr">
         <s:is>
-          <s:t>IC BUCK-BOOST CONV 24-SSOP</s:t>
+          <s:t>IC OPAMP DUAL -40-85 C 8-SOIC</s:t>
         </s:is>
       </s:c>
       <s:c r="G7" s="11" t="inlineStr">
         <s:is>
-          <s:t>24-SSOP</s:t>
+          <s:t>8-SOIC</s:t>
         </s:is>
       </s:c>
       <s:c r="H7" s="12" t="inlineStr">
         <s:is>
-          <s:t>SMD</s:t>
+          <s:t>DNS</s:t>
         </s:is>
       </s:c>
       <s:c r="I7" s="12"/>
     </s:row>
     <s:row r="8" s="1" customFormat="1" spans="1:9">
       <s:c r="A8" s="13">
-        <s:v>2</s:v>
+        <s:v>3</s:v>
       </s:c>
       <s:c r="B8" s="14" t="inlineStr">
         <s:is>
-          <s:t>U2,U4</s:t>
+          <s:t>U3</s:t>
         </s:is>
       </s:c>
       <s:c r="C8" s="13">
-        <s:v>2</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="D8" s="14" t="inlineStr">
         <s:is>
-          <s:t>Fairchild</s:t>
+          <s:t>ON</s:t>
         </s:is>
       </s:c>
       <s:c r="E8" s="14" t="inlineStr">
         <s:is>
-          <s:t>LM2904M</s:t>
+          <s:t>LM317MBDTG</s:t>
         </s:is>
       </s:c>
       <s:c r="F8" s="15" t="inlineStr">
         <s:is>
-          <s:t>IC OPAMP DUAL -40-85 C 8-SOIC</s:t>
+          <s:t>LM317M IC REG VOLT ADJ 500MA DPAK</s:t>
         </s:is>
       </s:c>
       <s:c r="G8" s="15" t="inlineStr">
         <s:is>
-          <s:t>8-SOIC</s:t>
+          <s:t>DPAK</s:t>
         </s:is>
       </s:c>
       <s:c r="H8" s="16" t="inlineStr">
         <s:is>
-          <s:t>DNS</s:t>
+          <s:t>SMD</s:t>
         </s:is>
       </s:c>
       <s:c r="I8" s="16"/>
     </s:row>
     <s:row r="9" spans="1:9">
       <s:c r="A9" s="9">
-        <s:v>3</s:v>
+        <s:v>4</s:v>
       </s:c>
       <s:c r="B9" s="10" t="inlineStr">
         <s:is>
-          <s:t>U3</s:t>
+          <s:t>U5</s:t>
         </s:is>
       </s:c>
       <s:c r="C9" s="9">
@@ -1655,22 +1688,22 @@
       </s:c>
       <s:c r="D9" s="10" t="inlineStr">
         <s:is>
-          <s:t>ON</s:t>
+          <s:t>Microchip</s:t>
         </s:is>
       </s:c>
       <s:c r="E9" s="10" t="inlineStr">
         <s:is>
-          <s:t>LM317MBDTG</s:t>
+          <s:t>PIC16F690-I/SS</s:t>
         </s:is>
       </s:c>
       <s:c r="F9" s="11" t="inlineStr">
         <s:is>
-          <s:t>LM317M IC REG VOLT ADJ 500MA DPAK</s:t>
+          <s:t>IC PIC MCU FLASH 4KX14 20SSOP</s:t>
         </s:is>
       </s:c>
       <s:c r="G9" s="11" t="inlineStr">
         <s:is>
-          <s:t>DPAK</s:t>
+          <s:t>20SSOP</s:t>
         </s:is>
       </s:c>
       <s:c r="H9" s="12" t="inlineStr">
@@ -1682,11 +1715,11 @@
     </s:row>
     <s:row r="10" spans="1:9">
       <s:c r="A10" s="9">
-        <s:v>4</s:v>
+        <s:v>5</s:v>
       </s:c>
       <s:c r="B10" s="10" t="inlineStr">
         <s:is>
-          <s:t>U5</s:t>
+          <s:t>Q1</s:t>
         </s:is>
       </s:c>
       <s:c r="C10" s="9">
@@ -1694,22 +1727,22 @@
       </s:c>
       <s:c r="D10" s="10" t="inlineStr">
         <s:is>
-          <s:t>Microchip</s:t>
+          <s:t>Diodes Inc</s:t>
         </s:is>
       </s:c>
       <s:c r="E10" s="10" t="inlineStr">
         <s:is>
-          <s:t>PIC16F690-I/SS</s:t>
+          <s:t>GBJ10005-F</s:t>
         </s:is>
       </s:c>
       <s:c r="F10" s="11" t="inlineStr">
         <s:is>
-          <s:t>IC PIC MCU FLASH 4KX14 20SSOP</s:t>
+          <s:t>RECT BRIDGE GPP 50V 10A GBJ</s:t>
         </s:is>
       </s:c>
       <s:c r="G10" s="11" t="inlineStr">
         <s:is>
-          <s:t>20SSOP</s:t>
+          <s:t>GBJ</s:t>
         </s:is>
       </s:c>
       <s:c r="H10" s="12" t="inlineStr">
@@ -1721,41 +1754,15 @@
     </s:row>
     <s:row r="11" spans="1:9">
       <s:c r="A11" s="9">
-        <s:v>5</s:v>
-      </s:c>
-      <s:c r="B11" s="10" t="inlineStr">
-        <s:is>
-          <s:t>Q1</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C11" s="9">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="D11" s="10" t="inlineStr">
-        <s:is>
-          <s:t>Diodes Inc</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E11" s="10" t="inlineStr">
-        <s:is>
-          <s:t>GBJ10005-F</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F11" s="11" t="inlineStr">
-        <s:is>
-          <s:t>RECT BRIDGE GPP 50V 10A GBJ</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G11" s="11" t="inlineStr">
-        <s:is>
-          <s:t>GBJ</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H11" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SMD</s:t>
-        </s:is>
-      </s:c>
+        <s:v>77</s:v>
+      </s:c>
+      <s:c r="B11" s="10"/>
+      <s:c r="C11" s="9"/>
+      <s:c r="D11" s="10"/>
+      <s:c r="E11" s="10"/>
+      <s:c r="F11" s="11"/>
+      <s:c r="G11" s="11"/>
+      <s:c r="H11" s="12"/>
       <s:c r="I11" s="12"/>
     </s:row>
     <s:row r="12" spans="1:9">
@@ -2148,11 +2155,7 @@
       </s:c>
       <s:c r="I21" s="12"/>
     </s:row>
-    <s:row r="22">
-      <s:c r="A22">
-        <s:v>1</s:v>
-      </s:c>
-    </s:row>
+    <s:row r="22"/>
     <s:row r="23"/>
     <s:row r="24" ht="13.5" spans="1:9">
       <s:c r="A24" s="19" t="inlineStr">
@@ -2170,7 +2173,9 @@
       <s:c r="I24" s="19"/>
     </s:row>
     <s:row r="25" ht="13.5" spans="1:9">
-      <s:c r="A25" s="19"/>
+      <s:c r="A25" s="19">
+        <s:v>3</s:v>
+      </s:c>
       <s:c r="B25" s="19"/>
       <s:c r="C25" s="19"/>
       <s:c r="D25" s="19"/>
